--- a/欠款账本_测试示例.xlsx
+++ b/欠款账本_测试示例.xlsx
@@ -5,7 +5,9 @@
   <sheets>
     <sheet name="欠款订单" sheetId="1" r:id="rId1"/>
     <sheet name="还款记录" sheetId="2" r:id="rId2"/>
-    <sheet name="汇总" sheetId="3" r:id="rId3"/>
+    <sheet name="退货记录" sheetId="3" r:id="rId3"/>
+    <sheet name="汇总" sheetId="4" r:id="rId4"/>
+    <sheet name="设置" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I73"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,146 +411,2125 @@
         <v>客户名称</v>
       </c>
       <c r="C1" t="str">
+        <v>订单号</v>
+      </c>
+      <c r="D1" t="str">
+        <v>货号</v>
+      </c>
+      <c r="E1" t="str">
         <v>单价</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>数量</v>
       </c>
-      <c r="E1" t="str">
-        <v>总额</v>
-      </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>小计</v>
+      </c>
+      <c r="H1" t="str">
         <v>已付</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>备注</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-01</v>
+        <v>2025-12-28</v>
       </c>
       <c r="B2" t="str">
-        <v>张三</v>
-      </c>
-      <c r="C2">
-        <v>12.5</v>
-      </c>
-      <c r="D2">
-        <v>20</v>
+        <v>郑老板</v>
+      </c>
+      <c r="C2" t="str">
+        <v>o86</v>
+      </c>
+      <c r="D2" t="str">
+        <v>ZB-1</v>
       </c>
       <c r="E2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F2">
-        <v>100</v>
-      </c>
-      <c r="G2" t="str">
-        <v>大米</v>
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>300</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="str">
+        <v>去年年底</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-09-02</v>
+        <v>2025-12-30</v>
       </c>
       <c r="B3" t="str">
-        <v>李四</v>
-      </c>
-      <c r="C3">
-        <v>35</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
+        <v>郑老板</v>
+      </c>
+      <c r="C3" t="str">
+        <v>o87</v>
+      </c>
+      <c r="D3" t="str">
+        <v>ZB-2</v>
       </c>
       <c r="E3">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="str">
-        <v>食用油</v>
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>300</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-09-03</v>
+        <v>2026-01-03</v>
       </c>
       <c r="B4" t="str">
-        <v>王五</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <v>15</v>
+        <v>郑老板</v>
+      </c>
+      <c r="C4" t="str">
+        <v>o88</v>
+      </c>
+      <c r="D4" t="str">
+        <v>ZB-3</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F4">
-        <v>50</v>
-      </c>
-      <c r="G4" t="str">
-        <v>面粉</v>
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>400</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="str">
+        <v>跨年后</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-09-05</v>
+        <v>2026-03-01</v>
       </c>
       <c r="B5" t="str">
         <v>张三</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="str">
+        <v>o3</v>
+      </c>
+      <c r="D5" t="str">
+        <v>ZS-01</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
         <v>20</v>
       </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>100</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" t="str">
-        <v>鸡蛋</v>
+      <c r="H5">
+        <v>50</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="B6" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C6" t="str">
+        <v>o4</v>
+      </c>
+      <c r="D6" t="str">
+        <v>ZS-02</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="B7" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C7" t="str">
+        <v>o5</v>
+      </c>
+      <c r="D7" t="str">
+        <v>ZS-03</v>
+      </c>
+      <c r="E7">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="B8" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C8" t="str">
+        <v>o6</v>
+      </c>
+      <c r="D8" t="str">
+        <v>ZS-04</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="B9" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C9" t="str">
+        <v>o7</v>
+      </c>
+      <c r="D9" t="str">
+        <v>ZS-05</v>
+      </c>
+      <c r="E9">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>28</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="B10" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C10" t="str">
+        <v>o8</v>
+      </c>
+      <c r="D10" t="str">
+        <v>ZS-06</v>
+      </c>
+      <c r="E10">
+        <v>15</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>30</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-03-07</v>
+      </c>
+      <c r="B11" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C11" t="str">
+        <v>o9</v>
+      </c>
+      <c r="D11" t="str">
+        <v>ZS-07</v>
+      </c>
+      <c r="E11">
+        <v>16</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>32</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="B12" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C12" t="str">
+        <v>o10</v>
+      </c>
+      <c r="D12" t="str">
+        <v>ZS-08</v>
+      </c>
+      <c r="E12">
+        <v>17</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>34</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="B13" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C13" t="str">
+        <v>o11</v>
+      </c>
+      <c r="D13" t="str">
+        <v>ZS-09</v>
+      </c>
+      <c r="E13">
+        <v>18</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>36</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="B14" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C14" t="str">
+        <v>o12</v>
+      </c>
+      <c r="D14" t="str">
+        <v>ZS-10</v>
+      </c>
+      <c r="E14">
+        <v>19</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>38</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="B15" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C15" t="str">
+        <v>o13</v>
+      </c>
+      <c r="D15" t="str">
+        <v>ZS-11</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>40</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="B16" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C16" t="str">
+        <v>o14</v>
+      </c>
+      <c r="D16" t="str">
+        <v>ZS-12</v>
+      </c>
+      <c r="E16">
+        <v>21</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>42</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-03-13</v>
+      </c>
+      <c r="B17" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C17" t="str">
+        <v>o15</v>
+      </c>
+      <c r="D17" t="str">
+        <v>ZS-13</v>
+      </c>
+      <c r="E17">
+        <v>22</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>44</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="B18" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C18" t="str">
+        <v>o16</v>
+      </c>
+      <c r="D18" t="str">
+        <v>ZS-14</v>
+      </c>
+      <c r="E18">
+        <v>23</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>46</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="B19" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C19" t="str">
+        <v>o17</v>
+      </c>
+      <c r="D19" t="str">
+        <v>ZS-15</v>
+      </c>
+      <c r="E19">
+        <v>24</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>48</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="B20" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C20" t="str">
+        <v>o18</v>
+      </c>
+      <c r="D20" t="str">
+        <v>ZS-16</v>
+      </c>
+      <c r="E20">
+        <v>25</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>50</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="B21" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C21" t="str">
+        <v>o19</v>
+      </c>
+      <c r="D21" t="str">
+        <v>ZS-17</v>
+      </c>
+      <c r="E21">
+        <v>26</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>52</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="B22" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C22" t="str">
+        <v>o20</v>
+      </c>
+      <c r="D22" t="str">
+        <v>ZS-18</v>
+      </c>
+      <c r="E22">
+        <v>27</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>54</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="B23" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C23" t="str">
+        <v>o21</v>
+      </c>
+      <c r="D23" t="str">
+        <v>ZS-19</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>56</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="B24" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C24" t="str">
+        <v>o22</v>
+      </c>
+      <c r="D24" t="str">
+        <v>ZS-20</v>
+      </c>
+      <c r="E24">
+        <v>29</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>58</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="B25" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C25" t="str">
+        <v>o23</v>
+      </c>
+      <c r="D25" t="str">
+        <v>ZS-21</v>
+      </c>
+      <c r="E25">
+        <v>30</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <v>60</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="B26" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C26" t="str">
+        <v>o24</v>
+      </c>
+      <c r="D26" t="str">
+        <v>ZS-22</v>
+      </c>
+      <c r="E26">
+        <v>31</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>62</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="B27" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C27" t="str">
+        <v>o25</v>
+      </c>
+      <c r="D27" t="str">
+        <v>ZS-23</v>
+      </c>
+      <c r="E27">
+        <v>32</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>64</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="B28" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C28" t="str">
+        <v>o26</v>
+      </c>
+      <c r="D28" t="str">
+        <v>ZS-24</v>
+      </c>
+      <c r="E28">
+        <v>33</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>66</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="B29" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C29" t="str">
+        <v>o27</v>
+      </c>
+      <c r="D29" t="str">
+        <v>ZS-25</v>
+      </c>
+      <c r="E29">
+        <v>34</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>68</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="B30" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C30" t="str">
+        <v>o28</v>
+      </c>
+      <c r="D30" t="str">
+        <v>ZS-26</v>
+      </c>
+      <c r="E30">
+        <v>35</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>70</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="B31" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C31" t="str">
+        <v>o29</v>
+      </c>
+      <c r="D31" t="str">
+        <v>ZS-27</v>
+      </c>
+      <c r="E31">
+        <v>36</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>72</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="B32" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C32" t="str">
+        <v>o30</v>
+      </c>
+      <c r="D32" t="str">
+        <v>ZS-28</v>
+      </c>
+      <c r="E32">
+        <v>37</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32">
+        <v>74</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-03-29</v>
+      </c>
+      <c r="B33" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C33" t="str">
+        <v>o31</v>
+      </c>
+      <c r="D33" t="str">
+        <v>ZS-29</v>
+      </c>
+      <c r="E33">
+        <v>38</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>76</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="B34" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C34" t="str">
+        <v>o32</v>
+      </c>
+      <c r="D34" t="str">
+        <v>ZS-30</v>
+      </c>
+      <c r="E34">
+        <v>40</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <v>80</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="str">
+        <v>两个货号</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="B35" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C35" t="str">
+        <v>o32</v>
+      </c>
+      <c r="D35" t="str">
+        <v>ZS-31</v>
+      </c>
+      <c r="E35">
+        <v>15</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35">
+        <v>60</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="B36" t="str">
+        <v>周姐</v>
+      </c>
+      <c r="C36" t="str">
+        <v>o84</v>
+      </c>
+      <c r="D36" t="str">
+        <v>ZJ-1</v>
+      </c>
+      <c r="E36">
+        <v>100</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36">
+        <v>200</v>
+      </c>
+      <c r="H36">
+        <v>200</v>
+      </c>
+      <c r="I36" t="str">
+        <v>已当场付清</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="B37" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C37" t="str">
+        <v>o36</v>
+      </c>
+      <c r="D37" t="str">
+        <v>LC-01</v>
+      </c>
+      <c r="E37">
+        <v>100</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>100</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B38" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C38" t="str">
+        <v>o37</v>
+      </c>
+      <c r="D38" t="str">
+        <v>LC-02</v>
+      </c>
+      <c r="E38">
+        <v>100</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>100</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="B39" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C39" t="str">
+        <v>o38</v>
+      </c>
+      <c r="D39" t="str">
+        <v>LC-03</v>
+      </c>
+      <c r="E39">
+        <v>100</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>100</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B40" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C40" t="str">
+        <v>o39</v>
+      </c>
+      <c r="D40" t="str">
+        <v>LC-04</v>
+      </c>
+      <c r="E40">
+        <v>100</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>100</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B41" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C41" t="str">
+        <v>o40</v>
+      </c>
+      <c r="D41" t="str">
+        <v>LC-05</v>
+      </c>
+      <c r="E41">
+        <v>100</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>100</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="B42" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C42" t="str">
+        <v>o41</v>
+      </c>
+      <c r="D42" t="str">
+        <v>LC-06</v>
+      </c>
+      <c r="E42">
+        <v>100</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>100</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="B43" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C43" t="str">
+        <v>o42</v>
+      </c>
+      <c r="D43" t="str">
+        <v>LC-07</v>
+      </c>
+      <c r="E43">
+        <v>100</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>100</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="B44" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C44" t="str">
+        <v>o43</v>
+      </c>
+      <c r="D44" t="str">
+        <v>LC-08</v>
+      </c>
+      <c r="E44">
+        <v>100</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>100</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="B45" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C45" t="str">
+        <v>o44</v>
+      </c>
+      <c r="D45" t="str">
+        <v>LC-09</v>
+      </c>
+      <c r="E45">
+        <v>100</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>100</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="B46" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C46" t="str">
+        <v>o45</v>
+      </c>
+      <c r="D46" t="str">
+        <v>LC-10</v>
+      </c>
+      <c r="E46">
+        <v>100</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>100</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="B47" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C47" t="str">
+        <v>o46</v>
+      </c>
+      <c r="D47" t="str">
+        <v>LC-11</v>
+      </c>
+      <c r="E47">
+        <v>100</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>100</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="B48" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C48" t="str">
+        <v>o47</v>
+      </c>
+      <c r="D48" t="str">
+        <v>LC-12</v>
+      </c>
+      <c r="E48">
+        <v>100</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>100</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-06-13</v>
+      </c>
+      <c r="B49" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C49" t="str">
+        <v>o48</v>
+      </c>
+      <c r="D49" t="str">
+        <v>LC-13</v>
+      </c>
+      <c r="E49">
+        <v>100</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>100</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-06-14</v>
+      </c>
+      <c r="B50" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C50" t="str">
+        <v>o49</v>
+      </c>
+      <c r="D50" t="str">
+        <v>LC-14</v>
+      </c>
+      <c r="E50">
+        <v>100</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>100</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B51" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C51" t="str">
+        <v>o50</v>
+      </c>
+      <c r="D51" t="str">
+        <v>LC-15</v>
+      </c>
+      <c r="E51">
+        <v>100</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>100</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-06-16</v>
+      </c>
+      <c r="B52" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C52" t="str">
+        <v>o51</v>
+      </c>
+      <c r="D52" t="str">
+        <v>LC-16</v>
+      </c>
+      <c r="E52">
+        <v>100</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>100</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-06-17</v>
+      </c>
+      <c r="B53" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C53" t="str">
+        <v>o52</v>
+      </c>
+      <c r="D53" t="str">
+        <v>LC-17</v>
+      </c>
+      <c r="E53">
+        <v>100</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>100</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="B54" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C54" t="str">
+        <v>o53</v>
+      </c>
+      <c r="D54" t="str">
+        <v>LC-18</v>
+      </c>
+      <c r="E54">
+        <v>100</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>100</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-06-19</v>
+      </c>
+      <c r="B55" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C55" t="str">
+        <v>o54</v>
+      </c>
+      <c r="D55" t="str">
+        <v>LC-19</v>
+      </c>
+      <c r="E55">
+        <v>100</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>100</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-06-20</v>
+      </c>
+      <c r="B56" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C56" t="str">
+        <v>o55</v>
+      </c>
+      <c r="D56" t="str">
+        <v>LC-D</v>
+      </c>
+      <c r="E56">
+        <v>12.5</v>
+      </c>
+      <c r="F56">
+        <v>0.5</v>
+      </c>
+      <c r="G56">
+        <v>6.25</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-06-21</v>
+      </c>
+      <c r="B57" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C57" t="str">
+        <v>o56</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57">
+        <v>100</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>100</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B58" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C58" t="str">
+        <v>o57</v>
+      </c>
+      <c r="D58" t="str">
+        <v>LC-A</v>
+      </c>
+      <c r="E58">
+        <v>100</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>100</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58" t="str">
+        <v>三样一起拿的</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B59" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C59" t="str">
+        <v>o57</v>
+      </c>
+      <c r="D59" t="str">
+        <v>LC-B</v>
+      </c>
+      <c r="E59">
+        <v>50</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <v>100</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B60" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C60" t="str">
+        <v>o57</v>
+      </c>
+      <c r="D60" t="str">
+        <v>LC-C</v>
+      </c>
+      <c r="E60">
+        <v>30</v>
+      </c>
+      <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="G60">
+        <v>90</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2026-08-20</v>
+      </c>
+      <c r="B61" t="str">
+        <v>孙师傅</v>
+      </c>
+      <c r="C61" t="str">
+        <v>o81</v>
+      </c>
+      <c r="D61" t="str">
+        <v>SS-1</v>
+      </c>
+      <c r="E61">
+        <v>10</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61">
+        <v>30</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61" t="str">
+        <v>上午</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2026-08-20</v>
+      </c>
+      <c r="B62" t="str">
+        <v>孙师傅</v>
+      </c>
+      <c r="C62" t="str">
+        <v>o81</v>
+      </c>
+      <c r="D62" t="str">
+        <v>SS-2</v>
+      </c>
+      <c r="E62">
+        <v>20</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62">
+        <v>40</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2026-08-20</v>
+      </c>
+      <c r="B63" t="str">
+        <v>孙师傅</v>
+      </c>
+      <c r="C63" t="str">
+        <v>o81</v>
+      </c>
+      <c r="D63" t="str">
+        <v>SS-3</v>
+      </c>
+      <c r="E63">
+        <v>5</v>
+      </c>
+      <c r="F63">
+        <v>10</v>
+      </c>
+      <c r="G63">
+        <v>50</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2026-08-20</v>
+      </c>
+      <c r="B64" t="str">
+        <v>孙师傅</v>
+      </c>
+      <c r="C64" t="str">
+        <v>o82</v>
+      </c>
+      <c r="D64" t="str">
+        <v>SS-4</v>
+      </c>
+      <c r="E64">
+        <v>15</v>
+      </c>
+      <c r="F64">
+        <v>4</v>
+      </c>
+      <c r="G64">
+        <v>60</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64" t="str">
+        <v>下午</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2026-08-20</v>
+      </c>
+      <c r="B65" t="str">
+        <v>孙师傅</v>
+      </c>
+      <c r="C65" t="str">
+        <v>o83</v>
+      </c>
+      <c r="D65" t="str">
+        <v>SS-5</v>
+      </c>
+      <c r="E65">
+        <v>8</v>
+      </c>
+      <c r="F65">
+        <v>5</v>
+      </c>
+      <c r="G65">
+        <v>40</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65" t="str">
+        <v>晚上</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="B66" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C66" t="str">
+        <v>o1</v>
+      </c>
+      <c r="D66" t="str">
+        <v>DM-01</v>
+      </c>
+      <c r="E66">
+        <v>12.5</v>
+      </c>
+      <c r="F66">
+        <v>20</v>
+      </c>
+      <c r="G66">
+        <v>250</v>
+      </c>
+      <c r="H66">
+        <v>100</v>
+      </c>
+      <c r="I66" t="str">
+        <v>大米</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2026-09-02</v>
+      </c>
+      <c r="B67" t="str">
+        <v>李四</v>
+      </c>
+      <c r="C67" t="str">
+        <v>o33</v>
+      </c>
+      <c r="D67" t="str">
+        <v>SY-11</v>
+      </c>
+      <c r="E67">
+        <v>35</v>
+      </c>
+      <c r="F67">
+        <v>3</v>
+      </c>
+      <c r="G67">
+        <v>105</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67" t="str">
+        <v>食用油</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2026-09-03</v>
+      </c>
+      <c r="B68" t="str">
+        <v>王五</v>
+      </c>
+      <c r="C68" t="str">
+        <v>o34</v>
+      </c>
+      <c r="D68" t="str">
+        <v>MF-07</v>
+      </c>
+      <c r="E68">
+        <v>8</v>
+      </c>
+      <c r="F68">
+        <v>15</v>
+      </c>
+      <c r="G68">
+        <v>120</v>
+      </c>
+      <c r="H68">
+        <v>50</v>
+      </c>
+      <c r="I68" t="str">
+        <v>面粉</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2026-09-05</v>
+      </c>
+      <c r="B69" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C69" t="str">
+        <v>o2</v>
+      </c>
+      <c r="D69" t="str">
+        <v>JJ-02</v>
+      </c>
+      <c r="E69">
+        <v>20</v>
+      </c>
+      <c r="F69">
+        <v>5</v>
+      </c>
+      <c r="G69">
+        <v>100</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69" t="str">
+        <v>鸡蛋</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
         <v>2026-09-06</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B70" t="str">
         <v>赵六</v>
       </c>
-      <c r="C6">
+      <c r="C70" t="str">
+        <v>o35</v>
+      </c>
+      <c r="D70" t="str">
+        <v>SC-21</v>
+      </c>
+      <c r="E70">
         <v>6.5</v>
       </c>
-      <c r="D6">
+      <c r="F70">
         <v>30</v>
       </c>
-      <c r="E6">
+      <c r="G70">
         <v>195</v>
       </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6" t="str">
+      <c r="H70">
+        <v>100</v>
+      </c>
+      <c r="I70" t="str">
         <v>蔬菜</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2026-09-13</v>
+      </c>
+      <c r="B71" t="str">
+        <v>钱老板</v>
+      </c>
+      <c r="C71" t="str">
+        <v>o90</v>
+      </c>
+      <c r="D71" t="str">
+        <v>QB-1</v>
+      </c>
+      <c r="E71">
+        <v>25</v>
+      </c>
+      <c r="F71">
+        <v>4</v>
+      </c>
+      <c r="G71">
+        <v>100</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71" t="str">
+        <v>昨天进的两样</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2026-09-13</v>
+      </c>
+      <c r="B72" t="str">
+        <v>钱老板</v>
+      </c>
+      <c r="C72" t="str">
+        <v>o90</v>
+      </c>
+      <c r="D72" t="str">
+        <v>QB-2</v>
+      </c>
+      <c r="E72">
+        <v>60</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>60</v>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="B73" t="str">
+        <v>钱老板</v>
+      </c>
+      <c r="C73" t="str">
+        <v>o91</v>
+      </c>
+      <c r="D73" t="str">
+        <v>QB-3</v>
+      </c>
+      <c r="E73">
+        <v>18</v>
+      </c>
+      <c r="F73">
+        <v>10</v>
+      </c>
+      <c r="G73">
+        <v>180</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73" t="str">
+        <v>今天补的货</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I73"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -566,56 +2547,1133 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-07</v>
+        <v>2026-01-05</v>
       </c>
       <c r="B2" t="str">
-        <v>张三</v>
+        <v>郑老板</v>
       </c>
       <c r="C2">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="D2" t="str">
-        <v>微信</v>
+        <v>结一部分</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-09-08</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B3" t="str">
-        <v>王五</v>
+        <v>老陈</v>
       </c>
       <c r="C3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D3" t="str">
-        <v>现金</v>
+        <v>微信</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-09-08</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B4" t="str">
-        <v>李四</v>
+        <v>老陈</v>
       </c>
       <c r="C4">
         <v>50</v>
       </c>
       <c r="D4" t="str">
+        <v>现金</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-07-03</v>
+      </c>
+      <c r="B5" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5" t="str">
         <v>微信</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-07-04</v>
+      </c>
+      <c r="B6" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C6">
+        <v>50</v>
+      </c>
+      <c r="D6" t="str">
+        <v>现金</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-07-05</v>
+      </c>
+      <c r="B7" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7" t="str">
+        <v>微信</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="B8" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+      <c r="D8" t="str">
+        <v>现金</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="B9" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C9">
+        <v>50</v>
+      </c>
+      <c r="D9" t="str">
+        <v>微信</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="B10" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C10">
+        <v>50</v>
+      </c>
+      <c r="D10" t="str">
+        <v>现金</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="B11" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C11">
+        <v>50</v>
+      </c>
+      <c r="D11" t="str">
+        <v>微信</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="B12" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C12">
+        <v>50</v>
+      </c>
+      <c r="D12" t="str">
+        <v>现金</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="B13" t="str">
+        <v>小吴</v>
+      </c>
+      <c r="C13">
+        <v>200</v>
+      </c>
+      <c r="D13" t="str">
+        <v>预付，还没拿货</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-07-11</v>
+      </c>
+      <c r="B14" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C14">
+        <v>50</v>
+      </c>
+      <c r="D14" t="str">
+        <v>微信</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-07-12</v>
+      </c>
+      <c r="B15" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C15">
+        <v>50</v>
+      </c>
+      <c r="D15" t="str">
+        <v>现金</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-07-13</v>
+      </c>
+      <c r="B16" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C16">
+        <v>50</v>
+      </c>
+      <c r="D16" t="str">
+        <v>微信</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-07-14</v>
+      </c>
+      <c r="B17" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C17">
+        <v>50</v>
+      </c>
+      <c r="D17" t="str">
+        <v>现金</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="B18" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C18">
+        <v>50</v>
+      </c>
+      <c r="D18" t="str">
+        <v>微信</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-07-16</v>
+      </c>
+      <c r="B19" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C19">
+        <v>50</v>
+      </c>
+      <c r="D19" t="str">
+        <v>现金</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="B20" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C20">
+        <v>50</v>
+      </c>
+      <c r="D20" t="str">
+        <v>微信</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-07-18</v>
+      </c>
+      <c r="B21" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C21">
+        <v>50</v>
+      </c>
+      <c r="D21" t="str">
+        <v>现金</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-07-19</v>
+      </c>
+      <c r="B22" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C22">
+        <v>50</v>
+      </c>
+      <c r="D22" t="str">
+        <v>微信</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-07-20</v>
+      </c>
+      <c r="B23" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C23">
+        <v>50</v>
+      </c>
+      <c r="D23" t="str">
+        <v>现金</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-07-21</v>
+      </c>
+      <c r="B24" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C24">
+        <v>50</v>
+      </c>
+      <c r="D24" t="str">
+        <v>微信</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-08-25</v>
+      </c>
+      <c r="B25" t="str">
+        <v>孙师傅</v>
+      </c>
+      <c r="C25">
+        <v>60</v>
+      </c>
+      <c r="D25" t="str">
+        <v>微信</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-08-25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>孙师傅</v>
+      </c>
+      <c r="C26">
+        <v>40</v>
+      </c>
+      <c r="D26" t="str">
+        <v>现金</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="B27" t="str">
+        <v>张三</v>
+      </c>
+      <c r="C27">
+        <v>150</v>
+      </c>
+      <c r="D27" t="str">
+        <v>微信</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="B28" t="str">
+        <v>李四</v>
+      </c>
+      <c r="C28">
+        <v>50</v>
+      </c>
+      <c r="D28" t="str">
+        <v>微信</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="B29" t="str">
+        <v>王五</v>
+      </c>
+      <c r="C29">
+        <v>70</v>
+      </c>
+      <c r="D29" t="str">
+        <v>现金</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="B30" t="str">
+        <v>钱老板</v>
+      </c>
+      <c r="C30">
+        <v>100</v>
+      </c>
+      <c r="D30" t="str">
+        <v>微信转账</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:H27"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>日期</v>
+      </c>
+      <c r="B1" t="str">
+        <v>客户名称</v>
+      </c>
+      <c r="C1" t="str">
+        <v>退货号</v>
+      </c>
+      <c r="D1" t="str">
+        <v>货号</v>
+      </c>
+      <c r="E1" t="str">
+        <v>单价</v>
+      </c>
+      <c r="F1" t="str">
+        <v>数量</v>
+      </c>
+      <c r="G1" t="str">
+        <v>小计</v>
+      </c>
+      <c r="H1" t="str">
+        <v>备注</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="B2" t="str">
+        <v>郑老板</v>
+      </c>
+      <c r="C2" t="str">
+        <v>t89</v>
+      </c>
+      <c r="D2" t="str">
+        <v>ZB-3</v>
+      </c>
+      <c r="E2">
+        <v>80</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>80</v>
+      </c>
+      <c r="H2" t="str">
+        <v>退一件</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="B3" t="str">
+        <v>周姐</v>
+      </c>
+      <c r="C3" t="str">
+        <v>t85</v>
+      </c>
+      <c r="D3" t="str">
+        <v>ZJ-1</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
+      <c r="H3" t="str">
+        <v>退一件</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="B4" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C4" t="str">
+        <v>t58</v>
+      </c>
+      <c r="D4" t="str">
+        <v>LC-01</v>
+      </c>
+      <c r="E4">
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>25</v>
+      </c>
+      <c r="H4" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-08-02</v>
+      </c>
+      <c r="B5" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C5" t="str">
+        <v>t59</v>
+      </c>
+      <c r="D5" t="str">
+        <v>LC-02</v>
+      </c>
+      <c r="E5">
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>25</v>
+      </c>
+      <c r="H5" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="B6" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C6" t="str">
+        <v>t60</v>
+      </c>
+      <c r="D6" t="str">
+        <v>LC-03</v>
+      </c>
+      <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>25</v>
+      </c>
+      <c r="H6" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-08-04</v>
+      </c>
+      <c r="B7" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C7" t="str">
+        <v>t61</v>
+      </c>
+      <c r="D7" t="str">
+        <v>LC-04</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>25</v>
+      </c>
+      <c r="H7" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-08-05</v>
+      </c>
+      <c r="B8" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C8" t="str">
+        <v>t62</v>
+      </c>
+      <c r="D8" t="str">
+        <v>LC-05</v>
+      </c>
+      <c r="E8">
+        <v>25</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>25</v>
+      </c>
+      <c r="H8" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="B9" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C9" t="str">
+        <v>t63</v>
+      </c>
+      <c r="D9" t="str">
+        <v>LC-06</v>
+      </c>
+      <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>25</v>
+      </c>
+      <c r="H9" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-08-07</v>
+      </c>
+      <c r="B10" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C10" t="str">
+        <v>t64</v>
+      </c>
+      <c r="D10" t="str">
+        <v>LC-07</v>
+      </c>
+      <c r="E10">
+        <v>25</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>25</v>
+      </c>
+      <c r="H10" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-08-08</v>
+      </c>
+      <c r="B11" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C11" t="str">
+        <v>t65</v>
+      </c>
+      <c r="D11" t="str">
+        <v>LC-08</v>
+      </c>
+      <c r="E11">
+        <v>25</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>25</v>
+      </c>
+      <c r="H11" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-08-09</v>
+      </c>
+      <c r="B12" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C12" t="str">
+        <v>t66</v>
+      </c>
+      <c r="D12" t="str">
+        <v>LC-09</v>
+      </c>
+      <c r="E12">
+        <v>25</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>25</v>
+      </c>
+      <c r="H12" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="B13" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C13" t="str">
+        <v>t67</v>
+      </c>
+      <c r="D13" t="str">
+        <v>LC-10</v>
+      </c>
+      <c r="E13">
+        <v>25</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>25</v>
+      </c>
+      <c r="H13" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-08-11</v>
+      </c>
+      <c r="B14" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C14" t="str">
+        <v>t68</v>
+      </c>
+      <c r="D14" t="str">
+        <v>LC-11</v>
+      </c>
+      <c r="E14">
+        <v>25</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>25</v>
+      </c>
+      <c r="H14" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-08-12</v>
+      </c>
+      <c r="B15" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C15" t="str">
+        <v>t69</v>
+      </c>
+      <c r="D15" t="str">
+        <v>LC-12</v>
+      </c>
+      <c r="E15">
+        <v>25</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>25</v>
+      </c>
+      <c r="H15" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-08-13</v>
+      </c>
+      <c r="B16" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C16" t="str">
+        <v>t70</v>
+      </c>
+      <c r="D16" t="str">
+        <v>LC-13</v>
+      </c>
+      <c r="E16">
+        <v>25</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>25</v>
+      </c>
+      <c r="H16" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-08-14</v>
+      </c>
+      <c r="B17" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C17" t="str">
+        <v>t71</v>
+      </c>
+      <c r="D17" t="str">
+        <v>LC-14</v>
+      </c>
+      <c r="E17">
+        <v>25</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>25</v>
+      </c>
+      <c r="H17" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-08-15</v>
+      </c>
+      <c r="B18" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C18" t="str">
+        <v>t72</v>
+      </c>
+      <c r="D18" t="str">
+        <v>LC-15</v>
+      </c>
+      <c r="E18">
+        <v>25</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>25</v>
+      </c>
+      <c r="H18" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-08-16</v>
+      </c>
+      <c r="B19" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C19" t="str">
+        <v>t73</v>
+      </c>
+      <c r="D19" t="str">
+        <v>LC-16</v>
+      </c>
+      <c r="E19">
+        <v>25</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>25</v>
+      </c>
+      <c r="H19" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="B20" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C20" t="str">
+        <v>t74</v>
+      </c>
+      <c r="D20" t="str">
+        <v>LC-17</v>
+      </c>
+      <c r="E20">
+        <v>25</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>25</v>
+      </c>
+      <c r="H20" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-08-18</v>
+      </c>
+      <c r="B21" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C21" t="str">
+        <v>t75</v>
+      </c>
+      <c r="D21" t="str">
+        <v>LC-18</v>
+      </c>
+      <c r="E21">
+        <v>25</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>25</v>
+      </c>
+      <c r="H21" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="B22" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C22" t="str">
+        <v>t76</v>
+      </c>
+      <c r="D22" t="str">
+        <v>LC-19</v>
+      </c>
+      <c r="E22">
+        <v>25</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>25</v>
+      </c>
+      <c r="H22" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-08-20</v>
+      </c>
+      <c r="B23" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C23" t="str">
+        <v>t77</v>
+      </c>
+      <c r="D23" t="str">
+        <v>LC-20</v>
+      </c>
+      <c r="E23">
+        <v>25</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>25</v>
+      </c>
+      <c r="H23" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-08-21</v>
+      </c>
+      <c r="B24" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C24" t="str">
+        <v>t78</v>
+      </c>
+      <c r="D24" t="str">
+        <v>LC-21</v>
+      </c>
+      <c r="E24">
+        <v>25</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>25</v>
+      </c>
+      <c r="H24" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-08-22</v>
+      </c>
+      <c r="B25" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C25" t="str">
+        <v>t79</v>
+      </c>
+      <c r="D25" t="str">
+        <v>LC-22</v>
+      </c>
+      <c r="E25">
+        <v>25</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>25</v>
+      </c>
+      <c r="H25" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-08-23</v>
+      </c>
+      <c r="B26" t="str">
+        <v>老陈</v>
+      </c>
+      <c r="C26" t="str">
+        <v>t80</v>
+      </c>
+      <c r="D26" t="str">
+        <v>LC-23</v>
+      </c>
+      <c r="E26">
+        <v>25</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>25</v>
+      </c>
+      <c r="H26" t="str">
+        <v>退货</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="B27" t="str">
+        <v>钱老板</v>
+      </c>
+      <c r="C27" t="str">
+        <v>t92</v>
+      </c>
+      <c r="D27" t="str">
+        <v>QB-2</v>
+      </c>
+      <c r="E27">
+        <v>60</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>60</v>
+      </c>
+      <c r="H27" t="str">
+        <v>退了个大的</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H27"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -628,6 +3686,9 @@
         <v>已还总额</v>
       </c>
       <c r="D1" t="str">
+        <v>退货总额</v>
+      </c>
+      <c r="E1" t="str">
         <v>未还金额</v>
       </c>
     </row>
@@ -636,60 +3697,201 @@
         <v>张三</v>
       </c>
       <c r="B2">
-        <v>350</v>
+        <v>1882</v>
       </c>
       <c r="C2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1582</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>李四</v>
+        <v>老陈</v>
       </c>
       <c r="B3">
-        <v>105</v>
+        <v>2296.25</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>1050</v>
       </c>
       <c r="D3">
-        <v>55</v>
+        <v>575</v>
+      </c>
+      <c r="E3">
+        <v>671.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>王五</v>
+        <v>郑老板</v>
       </c>
       <c r="B4">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="C4">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="E4">
+        <v>320</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>钱老板</v>
+      </c>
+      <c r="B5">
+        <v>340</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+      <c r="E5">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>孙师傅</v>
+      </c>
+      <c r="B6">
+        <v>220</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>赵六</v>
       </c>
-      <c r="B5">
+      <c r="B7">
         <v>195</v>
       </c>
-      <c r="C5">
-        <v>100</v>
-      </c>
-      <c r="D5">
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>李四</v>
+      </c>
+      <c r="B8">
+        <v>105</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>王五</v>
+      </c>
+      <c r="B9">
+        <v>120</v>
+      </c>
+      <c r="C9">
+        <v>120</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>周姐</v>
+      </c>
+      <c r="B10">
+        <v>200</v>
+      </c>
+      <c r="C10">
+        <v>200</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>小吴</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>200</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>-200</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>项目</v>
+      </c>
+      <c r="B1" t="str">
+        <v>值</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>店名</v>
+      </c>
+      <c r="B2" t="str">
+        <v>测试杂货店</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
   </ignoredErrors>
 </worksheet>
 </file>